--- a/experiment_results/wedos_grid/rtt_bursts_S3_atk1pct_wu500000_stage1a_rep1.xlsx
+++ b/experiment_results/wedos_grid/rtt_bursts_S3_atk1pct_wu500000_stage1a_rep1.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -553,12 +553,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -630,12 +630,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7466</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>92620</t>
+          <t>70999</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>113088</t>
+          <t>49333</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>71863</t>
+          <t>29774</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>51625</t>
+          <t>29095</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>50947</t>
+          <t>29095</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
